--- a/docs/backlog.xlsx
+++ b/docs/backlog.xlsx
@@ -1,26 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vikto\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vikto\Documents\HTL\3IHIF\WMC\room-food-docs\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{BDF87BFC-CB1A-47AA-9E6E-1FCDADF8D073}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0D5D314-F3AF-4161-8F37-8F79FA6152A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{22E5F82E-58E4-4701-95FD-1E96D258FD34}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{22E5F82E-58E4-4701-95FD-1E96D258FD34}"/>
   </bookViews>
   <sheets>
-    <sheet name="Backlog - Total" sheetId="1" r:id="rId1"/>
+    <sheet name="Total" sheetId="1" r:id="rId1"/>
+    <sheet name="Sprint 3" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="151">
   <si>
     <t>Title</t>
   </si>
@@ -431,6 +445,48 @@
   </si>
   <si>
     <t>Ingredient list functionality</t>
+  </si>
+  <si>
+    <t>Sprint 3</t>
+  </si>
+  <si>
+    <t>Display information when meal clicked</t>
+  </si>
+  <si>
+    <t>Fix account deleting</t>
+  </si>
+  <si>
+    <t>Improve room overview</t>
+  </si>
+  <si>
+    <t>Improve calendar design for room view</t>
+  </si>
+  <si>
+    <t>Room and room view functionality</t>
+  </si>
+  <si>
+    <t>Manage room members</t>
+  </si>
+  <si>
+    <t>Miscellaneous</t>
+  </si>
+  <si>
+    <t>Improve create room frontend</t>
+  </si>
+  <si>
+    <t>Testing</t>
+  </si>
+  <si>
+    <t>Basic recipe creation and overview</t>
+  </si>
+  <si>
+    <t>When adding a meal specify a recipe</t>
+  </si>
+  <si>
+    <t>Add responsible logic to select user</t>
+  </si>
+  <si>
+    <t>Database/website configuration</t>
   </si>
 </sst>
 </file>
@@ -2425,4 +2481,382 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C1E4160-01FB-4AB0-9800-ABD68DECDB8A}">
+  <dimension ref="A1:C33"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="32" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="44.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C6" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>138</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>139</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>110</v>
+      </c>
+      <c r="B9" t="s">
+        <v>111</v>
+      </c>
+      <c r="C9" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>67</v>
+      </c>
+      <c r="B10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C10" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>140</v>
+      </c>
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>141</v>
+      </c>
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>142</v>
+      </c>
+      <c r="B13" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>143</v>
+      </c>
+      <c r="B14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>110</v>
+      </c>
+      <c r="B15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C15" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>65</v>
+      </c>
+      <c r="B16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>96</v>
+      </c>
+      <c r="B17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>94</v>
+      </c>
+      <c r="B18" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>142</v>
+      </c>
+      <c r="B19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>144</v>
+      </c>
+      <c r="B20" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>145</v>
+      </c>
+      <c r="B21" t="s">
+        <v>22</v>
+      </c>
+      <c r="C21" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>56</v>
+      </c>
+      <c r="B22" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>110</v>
+      </c>
+      <c r="B23" t="s">
+        <v>111</v>
+      </c>
+      <c r="C23" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>62</v>
+      </c>
+      <c r="B24" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>134</v>
+      </c>
+      <c r="B25" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>146</v>
+      </c>
+      <c r="B26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>107</v>
+      </c>
+      <c r="B27" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>116</v>
+      </c>
+      <c r="B28" t="s">
+        <v>117</v>
+      </c>
+      <c r="C28" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>147</v>
+      </c>
+      <c r="B29" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>148</v>
+      </c>
+      <c r="B30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>149</v>
+      </c>
+      <c r="B31" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>110</v>
+      </c>
+      <c r="B32" t="s">
+        <v>111</v>
+      </c>
+      <c r="C32" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>150</v>
+      </c>
+      <c r="B33" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" t="s">
+        <v>137</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>